--- a/data/27September-89ers-v-Gold_Diggers.xlsx
+++ b/data/27September-89ers-v-Gold_Diggers.xlsx
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:N160"/>
   <sheetData>
     <row r="1">
@@ -479,8 +479,10 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
-        <v>18</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -635,8 +637,10 @@
       <c r="D19" t="s">
         <v>17</v>
       </c>
-      <c r="E19" t="s">
-        <v>18</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -885,8 +889,10 @@
       <c r="D39" t="s">
         <v>17</v>
       </c>
-      <c r="E39" t="s">
-        <v>44</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DGLG</t>
+        </is>
       </c>
       <c r="I39" t="s">
         <v>21</v>
@@ -1342,8 +1348,10 @@
       <c r="D80" t="s">
         <v>49</v>
       </c>
-      <c r="E80" t="s">
-        <v>69</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -1501,8 +1509,10 @@
       <c r="D92" t="s">
         <v>49</v>
       </c>
-      <c r="E92" t="s">
-        <v>69</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="F92" t="s">
         <v>81</v>
@@ -1694,8 +1704,10 @@
       <c r="D109" t="s">
         <v>17</v>
       </c>
-      <c r="E109" t="s">
-        <v>18</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="J109" t="s">
         <v>19</v>
@@ -1843,8 +1855,10 @@
       <c r="D125" t="s">
         <v>17</v>
       </c>
-      <c r="E125" t="s">
-        <v>44</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>DGLG</t>
+        </is>
       </c>
       <c r="J125" t="s">
         <v>22</v>
@@ -1890,8 +1904,10 @@
       <c r="D129" t="s">
         <v>95</v>
       </c>
-      <c r="E129" t="s">
-        <v>96</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
       </c>
       <c r="L129" t="s">
         <v>97</v>
@@ -1983,8 +1999,10 @@
       <c r="D138" t="s">
         <v>17</v>
       </c>
-      <c r="E138" t="s">
-        <v>18</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="L138" t="s">
         <v>101</v>
@@ -2099,8 +2117,10 @@
       <c r="D148" t="s">
         <v>49</v>
       </c>
-      <c r="E148" t="s">
-        <v>108</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>UCDCLC</t>
+        </is>
       </c>
       <c r="J148" t="s">
         <v>22</v>
